--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -2426,7 +2426,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>אינס</t>
+          <t>לי-אור</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>לי-אור</t>
+          <t>אינס</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>אנגלית – ארז</t>
+          <t>היסטוריה – אלי</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>היסטוריה – אלי</t>
+          <t>אנגלית – ארז</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך – אלי</t>
+          <t>היסטוריה – אלי</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -4115,9 +4115,9 @@
           <t>מגמות – מגמות</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך – אלי</t>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>אנגלית – ארז</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -4185,9 +4185,9 @@
           <t>מגמות – מגמות</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>אנגלית – ארז</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>היסטוריה – אלי</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>תנ"ך – אלי</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
           <t>היסטוריה – אלי</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>היסטוריה – אלי</t>
-        </is>
-      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>חינוך – אלי</t>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה – אלי</t>
+          <t>חינוך – אלי</t>
         </is>
       </c>
       <c r="G18" s="8" t="n"/>
@@ -4239,7 +4239,7 @@
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>חינוך – אלי</t>
+          <t>תנ"ך – אלי</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>גיאוגרפיה – אלי</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -4544,7 +4544,7 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>גיאוגרפיה – אלי</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>אנגלית – גלית</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>אנגלית – גלית</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>אנגלית – גלית</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>אנגלית – גלית</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>מתמטיקה – מורה חיצוני</t>
+          <t>מתמטיקה – הילה</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5080,15 +5080,15 @@
         <v>7</v>
       </c>
       <c r="B53" s="8" t="n"/>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>מתמטיקה – הילה</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>חסר מורה</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>היסטוריה – תמיר</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>ד מירי</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -5987,7 +5987,7 @@
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>ז אלי (תנ"ך)</t>
+          <t>ז אלי (היסטוריה)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -6010,7 +6010,7 @@
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ז אלי (תנ"ך)</t>
+          <t>ז נעמי (היסטוריה)</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -6035,7 +6035,11 @@
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr"/>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>ח גלית (גיאוגרפיה)</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
     </row>
@@ -6052,7 +6056,7 @@
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>ז נעמי (היסטוריה)</t>
+          <t>ז אלי (היסטוריה)</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -6064,7 +6068,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ז אלי (היסטוריה)</t>
+          <t>ז אלי (תנ"ך)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -6080,7 +6084,7 @@
       <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>ז אלי (היסטוריה)</t>
+          <t>ז אלי (חינוך)</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -6096,7 +6100,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>ז אלי (חינוך)</t>
+          <t>ז אלי (תנ"ך)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr"/>
@@ -6119,11 +6123,7 @@
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>ח גלית (גיאוגרפיה)</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
       <c r="D76" s="4" t="inlineStr"/>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>ז נעמי (אנגלית)</t>
+          <t>ז אלי (אנגלית)</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -6655,7 +6655,7 @@
       <c r="D78" s="4" t="inlineStr"/>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>ז אלי (אנגלית)</t>
+          <t>ז נעמי (אנגלית)</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>ט אסיף (אנגלית)</t>
+          <t>ט תמיר (אנגלית)</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
@@ -6792,7 +6792,11 @@
           <t>ט אסיף (אנגלית)</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>ט אסיף (אנגלית)</t>
+        </is>
+      </c>
       <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="inlineStr">
         <is>
@@ -6815,11 +6819,7 @@
           <t>ט תמיר (אנגלית)</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>ט תמיר (אנגלית)</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
       <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="inlineStr">
         <is>
@@ -7722,12 +7722,12 @@
     <row r="133">
       <c r="A133" s="15" t="inlineStr">
         <is>
-          <t>חסאן סראחן</t>
+          <t>הילה</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>סה"כ 10 ש'</t>
+          <t>סה"כ 14 ש'</t>
         </is>
       </c>
     </row>
@@ -7768,9 +7768,17 @@
         <v>1</v>
       </c>
       <c r="B135" s="4" t="inlineStr"/>
-      <c r="C135" s="4" t="inlineStr"/>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>ח גלית (מתמטיקה)</t>
+        </is>
+      </c>
       <c r="D135" s="4" t="inlineStr"/>
-      <c r="E135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>ט אסיף (מתמטיקה)</t>
+        </is>
+      </c>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="inlineStr"/>
     </row>
@@ -7779,13 +7787,17 @@
         <v>2</v>
       </c>
       <c r="B136" s="4" t="inlineStr"/>
-      <c r="C136" s="4" t="inlineStr"/>
-      <c r="D136" s="4" t="inlineStr"/>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>ח גלית (מתמטיקה)</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>ט תמיר (מתמטיקה)</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr"/>
       <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="inlineStr"/>
     </row>
@@ -7796,20 +7808,20 @@
       <c r="B137" s="4" t="inlineStr"/>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr"/>
+          <t>ט תמיר (מתמטיקה)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>ט אסיף (מתמטיקה)</t>
+        </is>
+      </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+          <t>ט תמיר (מתמטיקה)</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
@@ -7819,39 +7831,31 @@
       <c r="B138" s="4" t="inlineStr"/>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr"/>
+          <t>ט תמיר (מתמטיקה)</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>ט אסיף (מתמטיקה)</t>
+        </is>
+      </c>
       <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+      <c r="B139" s="4" t="inlineStr"/>
       <c r="C139" s="4" t="inlineStr"/>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ח גלית (מתמטיקה)</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
@@ -7866,10 +7870,14 @@
       <c r="C140" s="4" t="inlineStr"/>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr"/>
+          <t>ט תמיר (מתמטיקה)</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>ח גלית (מתמטיקה)</t>
+        </is>
+      </c>
       <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="inlineStr"/>
     </row>
@@ -7882,21 +7890,29 @@
           <t>אסיפת צוות</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr"/>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>ט אסיף (מתמטיקה)</t>
+        </is>
+      </c>
       <c r="D141" s="4" t="inlineStr"/>
-      <c r="E141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>ח גלית (מתמטיקה)</t>
+        </is>
+      </c>
       <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="15" t="inlineStr">
         <is>
-          <t>טלי ברינברג</t>
+          <t>חסאן סראחן</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>סה"כ 8 ש'</t>
+          <t>סה"כ 10 ש'</t>
         </is>
       </c>
     </row>
@@ -7948,13 +7964,13 @@
         <v>2</v>
       </c>
       <c r="B146" s="4" t="inlineStr"/>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+      <c r="C146" s="4" t="inlineStr"/>
       <c r="D146" s="4" t="inlineStr"/>
-      <c r="E146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
       <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="inlineStr"/>
     </row>
@@ -7965,16 +7981,20 @@
       <c r="B147" s="4" t="inlineStr"/>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
@@ -7984,31 +8004,39 @@
       <c r="B148" s="4" t="inlineStr"/>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr"/>
       <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B149" s="4" t="inlineStr"/>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
       <c r="C149" s="4" t="inlineStr"/>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
@@ -8020,14 +8048,10 @@
           <t>אסיפת צוות</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="C150" s="4" t="inlineStr"/>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>ב יערה</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr"/>
@@ -8052,12 +8076,12 @@
     <row r="153">
       <c r="A153" s="15" t="inlineStr">
         <is>
-          <t>יערה שיכט</t>
+          <t>טלי ברינברג</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>סה"כ 21 ש'</t>
+          <t>סה"כ 8 ש'</t>
         </is>
       </c>
     </row>
@@ -8097,135 +8121,79 @@
       <c r="A155" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="B155" s="4" t="inlineStr"/>
       <c r="C155" s="4" t="inlineStr"/>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="D155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
+      <c r="G155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr"/>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="B156" s="4" t="inlineStr"/>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
+      <c r="G156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="17" t="n">
         <v>3</v>
       </c>
       <c r="B157" s="4" t="inlineStr"/>
-      <c r="C157" s="4" t="inlineStr"/>
-      <c r="D157" s="4" t="inlineStr"/>
-      <c r="E157" s="4" t="inlineStr">
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>ב יערה</t>
         </is>
       </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t>ב יערה</t>
         </is>
       </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
+      <c r="G157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr"/>
-      <c r="D158" s="4" t="inlineStr"/>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="B158" s="4" t="inlineStr"/>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
+      <c r="G158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+      <c r="B159" s="4" t="inlineStr"/>
       <c r="C159" s="4" t="inlineStr"/>
-      <c r="D159" s="4" t="inlineStr"/>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
@@ -8237,13 +8205,17 @@
           <t>אסיפת צוות</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr"/>
-      <c r="D160" s="4" t="inlineStr"/>
-      <c r="E160" s="4" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>ב יערה</t>
         </is>
       </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr"/>
       <c r="F160" s="4" t="inlineStr"/>
       <c r="G160" s="4" t="inlineStr"/>
     </row>
@@ -8265,12 +8237,12 @@
     <row r="163">
       <c r="A163" s="15" t="inlineStr">
         <is>
-          <t>לי-אור שפירא</t>
+          <t>יערה שיכט</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>סה"כ 10 ש'</t>
+          <t>סה"כ 21 ש'</t>
         </is>
       </c>
     </row>
@@ -8310,91 +8282,135 @@
       <c r="A165" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B165" s="4" t="inlineStr"/>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="C165" s="4" t="inlineStr"/>
-      <c r="D165" s="4" t="inlineStr"/>
-      <c r="E165" s="4" t="inlineStr"/>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="inlineStr"/>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B166" s="4" t="inlineStr"/>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="C166" s="4" t="inlineStr"/>
-      <c r="D166" s="4" t="inlineStr"/>
-      <c r="E166" s="4" t="inlineStr"/>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr"/>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="17" t="n">
         <v>3</v>
       </c>
       <c r="B167" s="4" t="inlineStr"/>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr"/>
+      <c r="C167" s="4" t="inlineStr"/>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr"/>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B168" s="4" t="inlineStr"/>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr"/>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr"/>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr"/>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B169" s="4" t="inlineStr"/>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
       <c r="C169" s="4" t="inlineStr"/>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr"/>
-      <c r="F169" s="4" t="inlineStr"/>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="G169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
@@ -8407,12 +8423,12 @@
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr"/>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr"/>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="F170" s="4" t="inlineStr"/>
       <c r="G170" s="4" t="inlineStr"/>
     </row>
@@ -8434,12 +8450,12 @@
     <row r="173">
       <c r="A173" s="15" t="inlineStr">
         <is>
-          <t>לייה גור</t>
+          <t>לי-אור שפירא</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>סה"כ 21 ש'</t>
+          <t>סה"כ 10 ש'</t>
         </is>
       </c>
     </row>
@@ -8479,90 +8495,54 @@
       <c r="A175" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="B175" s="4" t="inlineStr"/>
+      <c r="C175" s="4" t="inlineStr"/>
+      <c r="D175" s="4" t="inlineStr"/>
       <c r="E175" s="4" t="inlineStr"/>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B176" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="B176" s="4" t="inlineStr"/>
+      <c r="C176" s="4" t="inlineStr"/>
+      <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="4" t="inlineStr"/>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="B177" s="4" t="inlineStr"/>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>ח גלית (תנ"ך)</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr"/>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
       <c r="E177" s="4" t="inlineStr"/>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="17" t="n">
@@ -8571,43 +8551,35 @@
       <c r="B178" s="4" t="inlineStr"/>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>ח גלית (תנ"ך)</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr"/>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
       <c r="E178" s="4" t="inlineStr"/>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr"/>
+      <c r="B179" s="4" t="inlineStr"/>
+      <c r="C179" s="4" t="inlineStr"/>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
       <c r="E179" s="4" t="inlineStr"/>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
@@ -8619,12 +8591,12 @@
           <t>אסיפת צוות</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C180" s="4" t="inlineStr"/>
+      <c r="D180" s="4" t="inlineStr">
         <is>
           <t>ג לייה</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr"/>
       <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr"/>
@@ -8647,12 +8619,12 @@
     <row r="183">
       <c r="A183" s="15" t="inlineStr">
         <is>
-          <t>מגמות</t>
+          <t>לייה גור</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>סה"כ 20 ש'</t>
+          <t>סה"כ 21 ש'</t>
         </is>
       </c>
     </row>
@@ -8692,87 +8664,135 @@
       <c r="A185" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B185" s="4" t="inlineStr"/>
-      <c r="C185" s="4" t="inlineStr"/>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
+          <t>ג לייה</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
-        </is>
-      </c>
-      <c r="G185" s="4" t="inlineStr"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B186" s="4" t="inlineStr"/>
-      <c r="C186" s="4" t="inlineStr"/>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
+          <t>ג לייה</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B187" s="4" t="inlineStr"/>
-      <c r="C187" s="4" t="inlineStr"/>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
-        </is>
-      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>ח גלית (תנ"ך)</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="4" t="inlineStr"/>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
-        </is>
-      </c>
-      <c r="G187" s="4" t="inlineStr"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="17" t="n">
         <v>4</v>
       </c>
       <c r="B188" s="4" t="inlineStr"/>
-      <c r="C188" s="4" t="inlineStr"/>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
-        </is>
-      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>ח גלית (תנ"ך)</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr"/>
       <c r="E188" s="4" t="inlineStr"/>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
-        </is>
-      </c>
-      <c r="G188" s="4" t="inlineStr"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B189" s="4" t="inlineStr"/>
-      <c r="C189" s="4" t="inlineStr"/>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="D189" s="4" t="inlineStr"/>
       <c r="E189" s="4" t="inlineStr"/>
-      <c r="F189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="G189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
@@ -8784,7 +8804,11 @@
           <t>אסיפת צוות</t>
         </is>
       </c>
-      <c r="C190" s="4" t="inlineStr"/>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="D190" s="4" t="inlineStr"/>
       <c r="E190" s="4" t="inlineStr"/>
       <c r="F190" s="4" t="inlineStr"/>
@@ -8808,12 +8832,12 @@
     <row r="193">
       <c r="A193" s="15" t="inlineStr">
         <is>
-          <t>מורה חיצוני</t>
+          <t>מגמות</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>סה"כ 13 ש'</t>
+          <t>סה"כ 20 ש'</t>
         </is>
       </c>
     </row>
@@ -8854,18 +8878,18 @@
         <v>1</v>
       </c>
       <c r="B195" s="4" t="inlineStr"/>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>ח גלית (מתמטיקה)</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr"/>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>ט תמיר (מתמטיקה)</t>
-        </is>
-      </c>
-      <c r="F195" s="4" t="inlineStr"/>
+      <c r="C195" s="4" t="inlineStr"/>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr"/>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
+        </is>
+      </c>
       <c r="G195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
@@ -8873,22 +8897,18 @@
         <v>2</v>
       </c>
       <c r="B196" s="4" t="inlineStr"/>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>ח גלית (מתמטיקה)</t>
-        </is>
-      </c>
+      <c r="C196" s="4" t="inlineStr"/>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>ט תמיר (מתמטיקה)</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>ט אסיף (מתמטיקה)</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr"/>
+          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr"/>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
+        </is>
+      </c>
       <c r="G196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
@@ -8896,22 +8916,18 @@
         <v>3</v>
       </c>
       <c r="B197" s="4" t="inlineStr"/>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>ט תמיר (מתמטיקה)</t>
-        </is>
-      </c>
+      <c r="C197" s="4" t="inlineStr"/>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>ט אסיף (מתמטיקה)</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>ח גלית (מתמטיקה)</t>
-        </is>
-      </c>
-      <c r="F197" s="4" t="inlineStr"/>
+          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr"/>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
+        </is>
+      </c>
       <c r="G197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
@@ -8919,18 +8935,18 @@
         <v>4</v>
       </c>
       <c r="B198" s="4" t="inlineStr"/>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>ט תמיר (מתמטיקה)</t>
-        </is>
-      </c>
+      <c r="C198" s="4" t="inlineStr"/>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>ט אסיף (מתמטיקה)</t>
+          <t>ז נעמי (מגמות), ז אלי (מגמות), ח גלית (מגמות)</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr"/>
-      <c r="F198" s="4" t="inlineStr"/>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>ט תמיר (מגמות), ט אסיף (מגמות)</t>
+        </is>
+      </c>
       <c r="G198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
@@ -8939,11 +8955,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr"/>
       <c r="C199" s="4" t="inlineStr"/>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>ח גלית (מתמטיקה)</t>
-        </is>
-      </c>
+      <c r="D199" s="4" t="inlineStr"/>
       <c r="E199" s="4" t="inlineStr"/>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="4" t="inlineStr"/>
@@ -8958,16 +8970,8 @@
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr"/>
-      <c r="D200" s="4" t="inlineStr">
-        <is>
-          <t>ט תמיר (מתמטיקה)</t>
-        </is>
-      </c>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>ח גלית (מתמטיקה)</t>
-        </is>
-      </c>
+      <c r="D200" s="4" t="inlineStr"/>
+      <c r="E200" s="4" t="inlineStr"/>
       <c r="F200" s="4" t="inlineStr"/>
       <c r="G200" s="4" t="inlineStr"/>
     </row>
@@ -11479,7 +11483,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>סה"כ 20 ש'</t>
+          <t>סה"כ 19 ש'</t>
         </is>
       </c>
     </row>
@@ -11672,11 +11676,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr"/>
       <c r="D341" s="4" t="inlineStr"/>
-      <c r="E341" s="4" t="inlineStr">
-        <is>
-          <t>ט אסיף (היסטוריה)</t>
-        </is>
-      </c>
+      <c r="E341" s="4" t="inlineStr"/>
       <c r="F341" s="4" t="inlineStr"/>
       <c r="G341" s="4" t="inlineStr"/>
     </row>
@@ -11888,7 +11888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12003,129 +12003,129 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>חסאן סראחן</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>חסן</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="20" t="inlineStr"/>
+      <c r="H3" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>דניאל צאל</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>דניאל</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>מחנך ג דניאל</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>חסאן סראחן</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>חסן</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="20" t="inlineStr"/>
-      <c r="H4" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>אנה זטרברג</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>אנה</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת א אנה</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>אביטל בוארון</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>אביטל</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ב אביטל</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <v>0</v>
+      <c r="K5" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>מרים</t>
+          <t>אנה זטרברג</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>מרים</t>
+          <t>אנה</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -12135,15 +12135,13 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
+          <t>מחנכת א אנה</t>
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>10</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
       <c r="G6" s="20" t="inlineStr"/>
       <c r="H6" s="20" t="inlineStr"/>
       <c r="I6" s="20" t="n">
@@ -12159,197 +12157,203 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>אביטל בוארון</t>
+          <t>יערה שיכט</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>אביטל</t>
+          <t>יערה</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>רביעי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ב אביטל</t>
+          <t>מחנכת ב יערה</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>יערה שיכט</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>יערה</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ב יערה</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4" t="n">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="J8" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>תמיר באום</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>תמיר</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="F9" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>סימה דוד</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>סימה</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>יסודי</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E10" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="n">
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J10" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="K10" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>דליה מרקוס</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>דליה</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>חמישי</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>מחנכת ג דליה</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>אינס אלקבץ</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>אינס</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד אינס</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F11" s="20" t="inlineStr"/>
-      <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
-      <c r="I11" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>תמיר באום</t>
+          <t>אינס אלקבץ</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>תמיר</t>
+          <t>אינס</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -12359,19 +12363,15 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+          <t>מחנכת ד אינס</t>
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>16</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F12" s="20" t="inlineStr"/>
       <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="n">
-        <v>4</v>
-      </c>
+      <c r="H12" s="20" t="inlineStr"/>
       <c r="I12" s="20" t="n">
         <v>24</v>
       </c>
@@ -12383,100 +12383,100 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>מירי בן עמי קריימר</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>מירי</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ד מירי</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>לייה גור</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>לייה</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="n">
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>פנינה קרפטי</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>פנינה</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת א פנינה</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
-      <c r="H14" s="20" t="inlineStr"/>
-      <c r="I14" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>מירי בן עמי קריימר</t>
+          <t>פנינה קרפטי</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>מירי</t>
+          <t>פנינה</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ד מירי</t>
+          <t>מחנכת א פנינה</t>
         </is>
       </c>
       <c r="E15" s="20" t="n">
@@ -12496,118 +12496,116 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>אסיף בניש</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>אסיף</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>גלית בצלאל</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
+      <c r="I16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>אלי אליהו מור</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>אלי</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J16" s="4" t="n">
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>אלי אליהו מור</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>אלי</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G17" s="20" t="inlineStr"/>
-      <c r="H17" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="20" t="n">
+      <c r="J18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="J17" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" s="20" t="n">
+      <c r="K18" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי קציר</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -12648,77 +12646,79 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>גלית בצלאל</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>גלית</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr"/>
-      <c r="F20" s="20" t="n">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>אסיף בניש</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>אסיף</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G20" s="20" t="inlineStr"/>
-      <c r="H20" s="20" t="inlineStr"/>
-      <c r="I20" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" s="20" t="n">
-        <v>0</v>
+      <c r="K20" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>תניה דניאלי</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>תניה</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="n">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>אורנה לוי</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>אורנה</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>שני, רביעי</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ו אורנה</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K21" s="20" t="n">
-        <v>0</v>
+      <c r="K21" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -12759,40 +12759,40 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>אורנה לוי</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>אורנה</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>שני, רביעי</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ו אורנה</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J23" s="4" t="n">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>תניה דניאלי</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>תניה</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="K23" s="4" t="n">
-        <v>1</v>
+      <c r="F23" s="20" t="inlineStr"/>
+      <c r="G23" s="20" t="inlineStr"/>
+      <c r="H23" s="20" t="inlineStr"/>
+      <c r="I23" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="J23" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -12948,12 +12948,12 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>מורה חיצוני</t>
+          <t>הילה</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>מורה חיצוני</t>
+          <t>הילה</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -12968,197 +12968,183 @@
       </c>
       <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>לי-אור שפירא</t>
+          <t>צבי טולצ'ינסקי</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>לי-אור</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>יסודי (עד 3 ימים)</t>
-        </is>
-      </c>
+          <t>צבי</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="19" t="inlineStr"/>
       <c r="E29" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" s="20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>9</v>
+      </c>
       <c r="G29" s="20" t="inlineStr"/>
       <c r="H29" s="20" t="inlineStr"/>
       <c r="I29" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J29" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K29" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>מאמי שימאזאקי</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>מאמי</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>אבי קרן צבי</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>אבי קרן צבי</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="19" t="inlineStr"/>
+      <c r="E30" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+      <c r="I30" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="J30" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="K30" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>טלי ברינברג</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>טלי</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="4" t="n">
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>יסודי (שני+שלישי בלבד)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K30" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>חגית אבידן</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>חגית</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>תל"ן אומנות (א+ד) · מגמה</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H31" s="20" t="n">
+      <c r="K31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="20" t="n">
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>שחר שלייסר</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>שחר</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>ראשון, חמישי, שישי</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="J31" s="20" t="n">
+      <c r="F32" s="20" t="inlineStr"/>
+      <c r="G32" s="20" t="inlineStr"/>
+      <c r="H32" s="20" t="inlineStr"/>
+      <c r="I32" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K31" s="20" t="n">
+      <c r="J32" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>טלי ברינברג</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>טלי</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>יסודי (שני+שלישי בלבד)</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>שחר שלייסר</t>
+          <t>חגית אבידן</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>חגית</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>ראשון, חמישי, שישי</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="n">
-        <v>10</v>
-      </c>
+          <t>תל"ן אומנות (א+ד) · מגמה</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr"/>
       <c r="F33" s="20" t="inlineStr"/>
-      <c r="G33" s="20" t="inlineStr"/>
-      <c r="H33" s="20" t="inlineStr"/>
+      <c r="G33" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I33" s="20" t="n">
         <v>10</v>
       </c>
@@ -13170,68 +13156,74 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>צבי טולצ'ינסקי</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>צבי</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr"/>
-      <c r="D34" s="19" t="inlineStr"/>
-      <c r="E34" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F34" s="20" t="n">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>מאמי שימאזאקי</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>מאמי</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="20" t="inlineStr"/>
-      <c r="I34" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J34" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" s="20" t="n">
-        <v>0</v>
+      <c r="I34" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>לי-אור שפירא</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>לי-אור</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>ראשון, שני, שלישי, שישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr"/>
-      <c r="F35" s="20" t="n">
-        <v>8</v>
-      </c>
+          <t>יסודי (עד 3 ימים)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="20" t="inlineStr"/>
       <c r="G35" s="20" t="inlineStr"/>
       <c r="H35" s="20" t="inlineStr"/>
       <c r="I35" s="20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J35" s="20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K35" s="20" t="n">
         <v>0</v>
@@ -13240,22 +13232,22 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>הדר קורצויל</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>הדר</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>ראשון, שני, שלישי, שישי</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -13275,115 +13267,152 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>הדר קורצויל</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>הדר</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="20" t="inlineStr"/>
+      <c r="I37" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J37" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>רובי קיסוס</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>רובי</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>מגמת אומנויות (שלישי בלבד)</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="n">
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>שיר אופיר</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>שיר</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>ראשון, שני, שלישי, רביעי, חמישי</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>שישי בלבד - עם ז אלי (ספרות/היסטוריה/חינוך)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr"/>
-      <c r="F38" s="20" t="n">
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="20" t="inlineStr"/>
-      <c r="I38" s="20" t="n">
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="20" t="inlineStr"/>
+      <c r="I39" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="J38" s="20" t="n">
+      <c r="J39" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="K38" s="20" t="n">
+      <c r="K39" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>אופיר</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>אופיר</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>ראשון, שני, רביעי, חמישי, שישי</t>
         </is>
       </c>
-      <c r="D39" s="21" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>מגמת חדשנות · שעות בכיתות ו בשלישי</t>
         </is>
       </c>
-      <c r="E39" s="22" t="n">
+      <c r="E40" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="22" t="inlineStr"/>
-      <c r="G39" s="22" t="inlineStr"/>
-      <c r="H39" s="22" t="n">
+      <c r="F40" s="22" t="inlineStr"/>
+      <c r="G40" s="22" t="inlineStr"/>
+      <c r="H40" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="22" t="n">
+      <c r="I40" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J39" s="22" t="n">
+      <c r="J40" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K39" s="22" t="n">
+      <c r="K40" s="22" t="n">
         <v>-3</v>
       </c>
     </row>

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12003,129 +12003,129 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>דניאל צאל</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>דניאל</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ג דניאל</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>חסאן סראחן</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>חסן</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
         </is>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E4" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="F4" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="20" t="inlineStr"/>
-      <c r="H3" s="20" t="n">
+      <c r="G4" s="20" t="inlineStr"/>
+      <c r="H4" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="I4" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="J4" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="K4" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>דניאל צאל</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>דניאל</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ג דניאל</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>אביטל בוארון</t>
+          <t>יערה שיכט</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>אביטל</t>
+          <t>יערה</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>רביעי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ב אביטל</t>
+          <t>מחנכת ב יערה</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>אנה זטרברג</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>אנה</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -12135,13 +12135,15 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א אנה</t>
+          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="G6" s="20" t="inlineStr"/>
       <c r="H6" s="20" t="inlineStr"/>
       <c r="I6" s="20" t="n">
@@ -12155,328 +12157,326 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>יערה שיכט</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>יערה</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>אנה זטרברג</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>אנה</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת א אנה</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>אביטל בוארון</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>אביטל</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ב אביטל</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>אינס אלקבץ</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>אינס</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ד אינס</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>דליה מרקוס</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>דליה</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ג דליה</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>סימה דוד</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>סימה</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>יסודי</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>תמיר באום</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>תמיר</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>לייה גור</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>לייה</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>פנינה קרפטי</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>פנינה</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>שני</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ב יערה</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K8" s="20" t="n">
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת א פנינה</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K14" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>תמיר באום</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>תמיר</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>סימה דוד</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>סימה</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>יסודי</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>דליה מרקוס</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>דליה</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ג דליה</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>אינס אלקבץ</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>אינס</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד אינס</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>מירי בן עמי קריימר</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>מירי</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד מירי</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>לייה גור</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>לייה</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>פנינה קרפטי</t>
+          <t>מירי בן עמי קריימר</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>פנינה</t>
+          <t>מירי</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א פנינה</t>
+          <t>מחנכת ד מירי</t>
         </is>
       </c>
       <c r="E15" s="20" t="n">
@@ -12498,30 +12498,32 @@
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>גלית בצלאל</t>
+          <t>אלי אליהו מור</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>גלית</t>
+          <t>אלי</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr"/>
       <c r="F16" s="20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I16" s="20" t="n">
         <v>20</v>
       </c>
@@ -12535,22 +12537,22 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>נעמי קציר</t>
+          <t>אסיף בניש</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>נעמי</t>
+          <t>אסיף</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -12558,81 +12560,81 @@
         <v>15</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I17" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K17" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" s="4" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>אלי אליהו מור</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>אלי</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>דני יהב בראון</t>
+          <t>גלית בצלאל</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>דני</t>
+          <t>גלית</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>מחנך ה דני (20 שעות)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="n">
+          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="F19" s="20" t="inlineStr"/>
       <c r="G19" s="20" t="inlineStr"/>
       <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="n">
@@ -12646,42 +12648,40 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>אסיף בניש</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>אסיף</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J20" s="4" t="n">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>דני יהב בראון</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>דני</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>מחנך ה דני (20 שעות)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K20" s="4" t="n">
-        <v>1</v>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="20" t="inlineStr"/>
+      <c r="H20" s="20" t="inlineStr"/>
+      <c r="I20" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -12724,22 +12724,22 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>צופיה חזון</t>
+          <t>תניה דניאלי</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>צופיה</t>
+          <t>תניה</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
+          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
         </is>
       </c>
       <c r="E22" s="20" t="n">
@@ -12761,22 +12761,22 @@
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>תניה דניאלי</t>
+          <t>צופיה חזון</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>תניה</t>
+          <t>צופיה</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
+          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
         </is>
       </c>
       <c r="E23" s="20" t="n">
@@ -12798,29 +12798,29 @@
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G24" s="20" t="inlineStr"/>
       <c r="H24" s="20" t="inlineStr"/>
       <c r="I24" s="20" t="n">
         <v>16</v>
@@ -12911,29 +12911,29 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="n">
+          <t>תל"ן חינוך סביבתי</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
       <c r="H27" s="20" t="inlineStr"/>
       <c r="I27" s="20" t="n">
         <v>16</v>
@@ -12985,22 +12985,20 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>צבי טולצ'ינסקי</t>
+          <t>אבי קרן צבי</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>צבי</t>
+          <t>אבי קרן צבי</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
       <c r="D29" s="19" t="inlineStr"/>
       <c r="E29" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F29" s="20" t="inlineStr"/>
       <c r="G29" s="20" t="inlineStr"/>
       <c r="H29" s="20" t="inlineStr"/>
       <c r="I29" s="20" t="n">
@@ -13016,20 +13014,22 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>אבי קרן צבי</t>
+          <t>צבי טולצ'ינסקי</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>אבי קרן צבי</t>
+          <t>צבי</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr"/>
       <c r="D30" s="19" t="inlineStr"/>
       <c r="E30" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="F30" s="20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>9</v>
+      </c>
       <c r="G30" s="20" t="inlineStr"/>
       <c r="H30" s="20" t="inlineStr"/>
       <c r="I30" s="20" t="n">
@@ -13043,40 +13043,40 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>טלי ברינברג</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>טלי</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>לי-אור שפירא</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>לי-אור</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>יסודי (שני+שלישי בלבד)</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="4" t="n">
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>יסודי (עד 3 ימים)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K31" s="4" t="n">
-        <v>2</v>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
+      <c r="I31" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -13117,137 +13117,137 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>טלי ברינברג</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>טלי</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>יסודי (שני+שלישי בלבד)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>חגית אבידן</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>חגית</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>חמישי</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>תל"ן אומנות (א+ד) · מגמה</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr"/>
-      <c r="F33" s="20" t="inlineStr"/>
-      <c r="G33" s="20" t="n">
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="H33" s="20" t="n">
+      <c r="H34" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="20" t="n">
+      <c r="I34" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="J33" s="20" t="n">
+      <c r="J34" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K33" s="20" t="n">
+      <c r="K34" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>מאמי שימאזאקי</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>מאמי</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="n">
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K34" s="4" t="n">
+      <c r="K35" s="4" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור שפירא</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>יסודי (עד 3 ימים)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="20" t="inlineStr"/>
-      <c r="I35" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J35" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K35" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר קורצויל</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>ראשון, שני, שלישי, שישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
+          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -13269,22 +13269,22 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>הדר קורצויל</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>הדר</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>ראשון, שני, שלישי, שישי</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12003,81 +12003,81 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>חסאן סראחן</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>חסן</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="20" t="inlineStr"/>
+      <c r="H3" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>דניאל צאל</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>דניאל</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>מחנך ג דניאל</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>חסאן סראחן</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>חסן</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="20" t="inlineStr"/>
-      <c r="H4" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -12231,40 +12231,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>אינס אלקבץ</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>אינס</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>תמיר באום</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>תמיר</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>שלישי</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד אינס</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n">
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0</v>
+      <c r="K9" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -12307,22 +12311,22 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>סימה דוד</t>
+          <t>אינס אלקבץ</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>סימה</t>
+          <t>אינס</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>יסודי</t>
+          <t>מחנכת ד אינס</t>
         </is>
       </c>
       <c r="E11" s="20" t="n">
@@ -12342,141 +12346,137 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>תמיר באום</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>תמיר</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="4" t="n">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>סימה דוד</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>סימה</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>יסודי</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>מירי בן עמי קריימר</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>מירי</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ד מירי</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>לייה גור</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>לייה</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="n">
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>פנינה קרפטי</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>פנינה</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת א פנינה</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
-      <c r="H14" s="20" t="inlineStr"/>
-      <c r="I14" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>מירי בן עמי קריימר</t>
+          <t>פנינה קרפטי</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>מירי</t>
+          <t>פנינה</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ד מירי</t>
+          <t>מחנכת א פנינה</t>
         </is>
       </c>
       <c r="E15" s="20" t="n">
@@ -12574,40 +12574,40 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי קציר</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="4" t="n">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>דני יהב בראון</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>דני</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>מחנך ה דני (20 שעות)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v>5</v>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -12648,114 +12648,114 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>דני יהב בראון</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>דני</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>מחנך ה דני (20 שעות)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="n">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F20" s="20" t="inlineStr"/>
-      <c r="G20" s="20" t="inlineStr"/>
-      <c r="H20" s="20" t="inlineStr"/>
-      <c r="I20" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" s="20" t="n">
+      <c r="K20" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>תניה דניאלי</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>תניה</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K21" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>אורנה לוי</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>אורנה</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>שני, רביעי</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>מחנכת ו אורנה</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="K22" s="4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>תניה דניאלי</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>תניה</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
-      <c r="I22" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J22" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K22" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -12798,30 +12798,32 @@
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יעל ליפשיץ</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יעל</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>16</v>
-      </c>
+          <t>תל"ן בישול (ד-ו) · מגמה</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
       <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>4</v>
+      </c>
       <c r="I24" s="20" t="n">
         <v>16</v>
       </c>
@@ -12835,29 +12837,29 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>הילית בן מאיר שטרן</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>הילית</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>תל"ן פיסול</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G25" s="20" t="inlineStr"/>
       <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="n">
         <v>16</v>
@@ -12872,32 +12874,30 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>יעל ליפשיץ</t>
+          <t>הילית בן מאיר שטרן</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>יעל</t>
+          <t>הילית</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>תל"ן בישול (ד-ו) · מגמה</t>
+          <t>תל"ן פיסול</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr"/>
       <c r="F26" s="20" t="inlineStr"/>
       <c r="G26" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>4</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr"/>
       <c r="I26" s="20" t="n">
         <v>16</v>
       </c>
@@ -13043,61 +13043,61 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור שפירא</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>מאמי שימאזאקי</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>מאמי</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>יסודי (עד 3 ימים)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="n">
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
-      <c r="I31" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K31" s="20" t="n">
-        <v>0</v>
+      <c r="K31" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>שחר שלייסר</t>
+          <t>לי-אור שפירא</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>לי-אור</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>ראשון, חמישי, שישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+          <t>יסודי (עד 3 ימים)</t>
         </is>
       </c>
       <c r="E32" s="20" t="n">
@@ -13117,116 +13117,116 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>חגית אבידן</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>חגית</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>תל"ן אומנות (א+ד) · מגמה</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr"/>
+      <c r="F33" s="20" t="inlineStr"/>
+      <c r="G33" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>טלי ברינברג</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>טלי</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>יסודי (שני+שלישי בלבד)</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E34" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="n">
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K33" s="4" t="n">
+      <c r="K34" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>חגית אבידן</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>חגית</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>תל"ן אומנות (א+ד) · מגמה</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr"/>
-      <c r="F34" s="20" t="inlineStr"/>
-      <c r="G34" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="20" t="n">
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>שחר שלייסר</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>שחר</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>ראשון, חמישי, שישי</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="J34" s="20" t="n">
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
+      <c r="I35" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K34" s="20" t="n">
+      <c r="J35" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>מאמי שימאזאקי</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>מאמי</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="36">

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12003,157 +12003,157 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>דניאל צאל</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>דניאל</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ג דניאל</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>חסאן סראחן</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>חסן</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
         </is>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E4" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="F4" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="20" t="inlineStr"/>
-      <c r="H3" s="20" t="n">
+      <c r="G4" s="20" t="inlineStr"/>
+      <c r="H4" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="I4" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="J4" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="K4" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>דניאל צאל</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>דניאל</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ג דניאל</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>יערה שיכט</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>יערה</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>שני</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>מחנכת ב יערה</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J6" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -12233,34 +12233,30 @@
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>תמיר באום</t>
+          <t>דליה מרקוס</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>תמיר</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+          <t>מחנכת ג דליה</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="n">
         <v>23</v>
       </c>
@@ -12272,40 +12268,40 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>דליה מרקוס</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>דליה</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ג דליה</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J10" s="4" t="n">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>סימה דוד</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>סימה</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>יסודי</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>1</v>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -12346,137 +12342,141 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>סימה דוד</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>סימה</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>יסודי</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>תמיר באום</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>תמיר</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>לייה גור</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>לייה</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>פנינה קרפטי</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>פנינה</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת א פנינה</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K14" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>מירי בן עמי קריימר</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>מירי</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד מירי</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>לייה גור</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>לייה</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>פנינה קרפטי</t>
+          <t>מירי בן עמי קריימר</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>פנינה</t>
+          <t>מירי</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א פנינה</t>
+          <t>מחנכת ד מירי</t>
         </is>
       </c>
       <c r="E15" s="20" t="n">
@@ -12496,42 +12496,40 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>אלי אליהו מור</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>אלי</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="20" t="n">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="J16" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>0</v>
+      <c r="K16" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -12576,30 +12574,32 @@
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>דני יהב בראון</t>
+          <t>אלי אליהו מור</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>דני</t>
+          <t>אלי</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>מחנך ה דני (20 שעות)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="F18" s="20" t="inlineStr"/>
+          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="n">
+        <v>18</v>
+      </c>
       <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I18" s="20" t="n">
         <v>20</v>
       </c>
@@ -12648,40 +12648,40 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>נעמי קציר</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>נעמי</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J20" s="4" t="n">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>דני יהב בראון</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>דני</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>מחנך ה דני (20 שעות)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K20" s="4" t="n">
-        <v>5</v>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="20" t="inlineStr"/>
+      <c r="H20" s="20" t="inlineStr"/>
+      <c r="I20" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -12722,108 +12722,106 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>צופיה חזון</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>צופיה</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
+      <c r="I22" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="J22" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K22" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>אורנה לוי</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>אורנה</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>שני, רביעי</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>מחנכת ו אורנה</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="n">
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="K23" s="4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>צופיה חזון</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>צופיה</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="F23" s="20" t="inlineStr"/>
-      <c r="G23" s="20" t="inlineStr"/>
-      <c r="H23" s="20" t="inlineStr"/>
-      <c r="I23" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J23" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K23" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>יעל ליפשיץ</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>יעל</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>תל"ן בישול (ד-ו) · מגמה</t>
+          <t>תל"ן חינוך סביבתי</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
       <c r="F24" s="20" t="inlineStr"/>
       <c r="G24" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>4</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr"/>
       <c r="I24" s="20" t="n">
         <v>16</v>
       </c>
@@ -12911,30 +12909,32 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>יעל ליפשיץ</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>יעל</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
+          <t>תל"ן בישול (ד-ו) · מגמה</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
       <c r="F27" s="20" t="inlineStr"/>
       <c r="G27" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="H27" s="20" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>4</v>
+      </c>
       <c r="I27" s="20" t="n">
         <v>16</v>
       </c>
@@ -13043,108 +13043,106 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>מאמי שימאזאקי</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>מאמי</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>לי-אור שפירא</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>לי-אור</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="4" t="n">
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>יסודי (עד 3 ימים)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K31" s="4" t="n">
-        <v>6</v>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
+      <c r="I31" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור שפירא</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>טלי ברינברג</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>טלי</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>יסודי (עד 3 ימים)</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="n">
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>יסודי (שני+שלישי בלבד)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F32" s="20" t="inlineStr"/>
-      <c r="G32" s="20" t="inlineStr"/>
-      <c r="H32" s="20" t="inlineStr"/>
-      <c r="I32" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K32" s="20" t="n">
-        <v>0</v>
+      <c r="K32" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>חגית אבידן</t>
+          <t>שחר שלייסר</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>חגית</t>
+          <t>שחר</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>ראשון, חמישי, שישי</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>תל"ן אומנות (א+ד) · מגמה</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr"/>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="F33" s="20" t="inlineStr"/>
-      <c r="G33" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H33" s="20" t="n">
-        <v>2</v>
-      </c>
+      <c r="G33" s="20" t="inlineStr"/>
+      <c r="H33" s="20" t="inlineStr"/>
       <c r="I33" s="20" t="n">
         <v>10</v>
       </c>
@@ -13158,12 +13156,12 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>טלי ברינברג</t>
+          <t>מאמי שימאזאקי</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>טלי</t>
+          <t>מאמי</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -13173,52 +13171,54 @@
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>יסודי (שני+שלישי בלבד)</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>8</v>
-      </c>
+          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>שחר שלייסר</t>
+          <t>חגית אבידן</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>חגית</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>ראשון, חמישי, שישי</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>10</v>
-      </c>
+          <t>תל"ן אומנות (א+ד) · מגמה</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr"/>
       <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I35" s="20" t="n">
         <v>10</v>
       </c>
@@ -13232,22 +13232,22 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>הדר קורצויל</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>הדר</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>ראשון, שני, שלישי, שישי</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -13269,22 +13269,22 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר קורצויל</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>ראשון, שני, שלישי, שישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
+          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12083,12 +12083,12 @@
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>מרים</t>
+          <t>אנה זטרברג</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>מרים</t>
+          <t>אנה</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -12098,15 +12098,13 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
+          <t>מחנכת א אנה</t>
         </is>
       </c>
       <c r="E5" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>10</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr"/>
       <c r="G5" s="20" t="inlineStr"/>
       <c r="H5" s="20" t="inlineStr"/>
       <c r="I5" s="20" t="n">
@@ -12122,49 +12120,49 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>יערה שיכט</t>
+          <t>אביטל בוארון</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>יערה</t>
+          <t>אביטל</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>רביעי</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ב יערה</t>
+          <t>מחנכת ב אביטל</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>אנה זטרברג</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>אנה</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -12174,13 +12172,15 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א אנה</t>
+          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
         </is>
       </c>
       <c r="E7" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="G7" s="20" t="inlineStr"/>
       <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="n">
@@ -12196,38 +12196,38 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>אביטל בוארון</t>
+          <t>יערה שיכט</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>אביטל</t>
+          <t>יערה</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>רביעי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ב אביטל</t>
+          <t>מחנכת ב יערה</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -12383,42 +12383,40 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>לייה גור</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>לייה</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J13" s="4" t="n">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>מירי בן עמי קריימר</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>מירי</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ד מירי</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>2</v>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -12459,61 +12457,63 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>מירי בן עמי קריימר</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>מירי</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד מירי</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="n">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>לייה גור</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>לייה</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J15" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>0</v>
+      <c r="K15" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>נעמי קציר</t>
+          <t>אסיף בניש</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>נעמי</t>
+          <t>אסיף</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -12521,85 +12521,83 @@
         <v>15</v>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I16" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>אסיף בניש</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>אסיף</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J17" s="4" t="n">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>גלית בצלאל</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>1</v>
+      <c r="G17" s="20" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+      <c r="I17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>אלי אליהו מור</t>
+          <t>דני יהב בראון</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>אלי</t>
+          <t>דני</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="n">
-        <v>18</v>
-      </c>
+          <t>מחנך ה דני (20 שעות)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="20" t="inlineStr"/>
       <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="n">
-        <v>2</v>
-      </c>
+      <c r="H18" s="20" t="inlineStr"/>
       <c r="I18" s="20" t="n">
         <v>20</v>
       </c>
@@ -12613,30 +12611,32 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>גלית בצלאל</t>
+          <t>אלי אליהו מור</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>גלית</t>
+          <t>אלי</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr"/>
       <c r="F19" s="20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I19" s="20" t="n">
         <v>20</v>
       </c>
@@ -12648,98 +12648,98 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>דני יהב בראון</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>דני</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>מחנך ה דני (20 שעות)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="n">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F20" s="20" t="inlineStr"/>
-      <c r="G20" s="20" t="inlineStr"/>
-      <c r="H20" s="20" t="inlineStr"/>
-      <c r="I20" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" s="20" t="n">
-        <v>0</v>
+      <c r="K20" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>תניה דניאלי</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>תניה</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="n">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>אורנה לוי</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>אורנה</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>שני, רביעי</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ו אורנה</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K21" s="20" t="n">
-        <v>0</v>
+      <c r="K21" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>צופיה חזון</t>
+          <t>תניה דניאלי</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>צופיה</t>
+          <t>תניה</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
+          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
         </is>
       </c>
       <c r="E22" s="20" t="n">
@@ -12759,51 +12759,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>אורנה לוי</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>אורנה</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>שני, רביעי</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ו אורנה</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J23" s="4" t="n">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>צופיה חזון</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>צופיה</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="K23" s="4" t="n">
-        <v>1</v>
+      <c r="F23" s="20" t="inlineStr"/>
+      <c r="G23" s="20" t="inlineStr"/>
+      <c r="H23" s="20" t="inlineStr"/>
+      <c r="I23" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="J23" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>הילית בן מאיר שטרן</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>הילית</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
+          <t>תל"ן פיסול</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -12835,30 +12835,32 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יעל ליפשיץ</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יעל</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>16</v>
-      </c>
+          <t>תל"ן בישול (ד-ו) · מגמה</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
       <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>4</v>
+      </c>
       <c r="I25" s="20" t="n">
         <v>16</v>
       </c>
@@ -12872,29 +12874,29 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>הילית בן מאיר שטרן</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>הילית</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>תל"ן פיסול</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F26" s="20" t="inlineStr"/>
-      <c r="G26" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G26" s="20" t="inlineStr"/>
       <c r="H26" s="20" t="inlineStr"/>
       <c r="I26" s="20" t="n">
         <v>16</v>
@@ -12909,32 +12911,30 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>יעל ליפשיץ</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>יעל</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>תל"ן בישול (ד-ו) · מגמה</t>
+          <t>תל"ן חינוך סביבתי</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
       <c r="F27" s="20" t="inlineStr"/>
       <c r="G27" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>4</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H27" s="20" t="inlineStr"/>
       <c r="I27" s="20" t="n">
         <v>16</v>
       </c>
@@ -13045,30 +13045,32 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>לי-אור שפירא</t>
+          <t>חגית אבידן</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>לי-אור</t>
+          <t>חגית</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>יסודי (עד 3 ימים)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>10</v>
-      </c>
+          <t>תל"ן אומנות (א+ד) · מגמה</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr"/>
       <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I31" s="20" t="n">
         <v>10</v>
       </c>
@@ -13082,12 +13084,12 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>טלי ברינברג</t>
+          <t>מאמי שימאזאקי</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>טלי</t>
+          <t>מאמי</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -13097,44 +13099,44 @@
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>יסודי (שני+שלישי בלבד)</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>8</v>
-      </c>
+          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I32" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>שחר שלייסר</t>
+          <t>לי-אור שפירא</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>לי-אור</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>ראשון, חמישי, שישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+          <t>יסודי (עד 3 ימים)</t>
         </is>
       </c>
       <c r="E33" s="20" t="n">
@@ -13156,12 +13158,12 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>מאמי שימאזאקי</t>
+          <t>טלי ברינברג</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>מאמי</t>
+          <t>טלי</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -13171,54 +13173,52 @@
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
+          <t>יסודי (שני+שלישי בלבד)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>חגית אבידן</t>
+          <t>שחר שלייסר</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>חגית</t>
+          <t>שחר</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>ראשון, חמישי, שישי</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>תל"ן אומנות (א+ד) · מגמה</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr"/>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H35" s="20" t="n">
-        <v>2</v>
-      </c>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
       <c r="I35" s="20" t="n">
         <v>10</v>
       </c>

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12003,92 +12003,92 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>חסאן סראחן</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>חסן</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="20" t="inlineStr"/>
+      <c r="H3" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>דניאל צאל</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>דניאל</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>מחנך ג דניאל</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>חסאן סראחן</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>חסן</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="20" t="inlineStr"/>
-      <c r="H4" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>אנה זטרברג</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>אנה</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -12098,13 +12098,15 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א אנה</t>
+          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
         </is>
       </c>
       <c r="E5" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="F5" s="20" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="G5" s="20" t="inlineStr"/>
       <c r="H5" s="20" t="inlineStr"/>
       <c r="I5" s="20" t="n">
@@ -12157,12 +12159,12 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>מרים</t>
+          <t>אנה זטרברג</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>מרים</t>
+          <t>אנה</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -12172,15 +12174,13 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
+          <t>מחנכת א אנה</t>
         </is>
       </c>
       <c r="E7" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>10</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr"/>
       <c r="G7" s="20" t="inlineStr"/>
       <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="n">
@@ -12270,22 +12270,22 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>סימה דוד</t>
+          <t>אינס אלקבץ</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>סימה</t>
+          <t>אינס</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>יסודי</t>
+          <t>מחנכת ד אינס</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
@@ -12307,22 +12307,22 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>אינס אלקבץ</t>
+          <t>סימה דוד</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>אינס</t>
+          <t>סימה</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ד אינס</t>
+          <t>יסודי</t>
         </is>
       </c>
       <c r="E11" s="20" t="n">
@@ -12420,182 +12420,180 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>לייה גור</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>לייה</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>פנינה קרפטי</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>פנינה</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>שני</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>מחנכת א פנינה</t>
         </is>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E15" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
-      <c r="H14" s="20" t="inlineStr"/>
-      <c r="I14" s="20" t="n">
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="J14" s="20" t="n">
+      <c r="J15" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="K14" s="20" t="n">
+      <c r="K15" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>לייה גור</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>לייה</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>אסיף בניש</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>אסיף</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="n">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>דני יהב בראון</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>דני</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>מחנך ה דני (20 שעות)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
+      <c r="I16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J16" s="4" t="n">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>גלית בצלאל</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>גלית</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="G17" s="20" t="inlineStr"/>
-      <c r="H17" s="20" t="inlineStr"/>
-      <c r="I17" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>0</v>
+      <c r="K17" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>דני יהב בראון</t>
+          <t>גלית בצלאל</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>דני</t>
+          <t>גלית</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>מחנך ה דני (20 שעות)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="n">
+          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="20" t="inlineStr"/>
       <c r="G18" s="20" t="inlineStr"/>
       <c r="H18" s="20" t="inlineStr"/>
       <c r="I18" s="20" t="n">
@@ -12609,153 +12607,155 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>אסיף בניש</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>אסיף</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>אלי אליהו מור</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>אלי</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr"/>
-      <c r="F19" s="20" t="n">
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="n">
+      <c r="G20" s="20" t="inlineStr"/>
+      <c r="H20" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="20" t="n">
+      <c r="I20" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="J19" s="20" t="n">
+      <c r="J20" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K19" s="20" t="n">
+      <c r="K20" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>נעמי קציר</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>נעמי</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>תניה דניאלי</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>תניה</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>חמישי</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K21" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>אורנה לוי</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>אורנה</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>שני, רביעי</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>מחנכת ו אורנה</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="K22" s="4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>תניה דניאלי</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>תניה</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
-      <c r="I22" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J22" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K22" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -12874,29 +12874,29 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="n">
+          <t>תל"ן חינוך סביבתי</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
+      <c r="G26" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="F26" s="20" t="inlineStr"/>
-      <c r="G26" s="20" t="inlineStr"/>
       <c r="H26" s="20" t="inlineStr"/>
       <c r="I26" s="20" t="n">
         <v>16</v>
@@ -12911,29 +12911,29 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G27" s="20" t="inlineStr"/>
       <c r="H27" s="20" t="inlineStr"/>
       <c r="I27" s="20" t="n">
         <v>16</v>
@@ -12985,20 +12985,22 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>אבי קרן צבי</t>
+          <t>צבי טולצ'ינסקי</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>אבי קרן צבי</t>
+          <t>צבי</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
       <c r="D29" s="19" t="inlineStr"/>
       <c r="E29" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="F29" s="20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>9</v>
+      </c>
       <c r="G29" s="20" t="inlineStr"/>
       <c r="H29" s="20" t="inlineStr"/>
       <c r="I29" s="20" t="n">
@@ -13014,22 +13016,20 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>צבי טולצ'ינסקי</t>
+          <t>אבי קרן צבי</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>צבי</t>
+          <t>אבי קרן צבי</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr"/>
       <c r="D30" s="19" t="inlineStr"/>
       <c r="E30" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F30" s="20" t="inlineStr"/>
       <c r="G30" s="20" t="inlineStr"/>
       <c r="H30" s="20" t="inlineStr"/>
       <c r="I30" s="20" t="n">
@@ -13082,40 +13082,40 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>מאמי שימאזאקי</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>מאמי</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="4" t="n">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>שחר שלייסר</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>שחר</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>ראשון, חמישי, שישי</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K32" s="4" t="n">
-        <v>6</v>
+      <c r="F32" s="20" t="inlineStr"/>
+      <c r="G32" s="20" t="inlineStr"/>
+      <c r="H32" s="20" t="inlineStr"/>
+      <c r="I32" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -13193,61 +13193,61 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>שחר שלייסר</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>שחר</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>ראשון, חמישי, שישי</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="n">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>מאמי שימאזאקי</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>מאמי</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="20" t="inlineStr"/>
-      <c r="I35" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J35" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K35" s="20" t="n">
-        <v>0</v>
+      <c r="K35" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר קורצויל</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>ראשון, שני, שלישי, שישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
+          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -13269,22 +13269,22 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>הדר קורצויל</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>הדר</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>ראשון, שני, שלישי, שישי</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>
